--- a/FileTypeMap.xlsx
+++ b/FileTypeMap.xlsx
@@ -1,176 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksullivan/Documents/MVP1/Profix Projects/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F92D5694-5A29-D047-8B5A-9782BF4A021D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{68E5AA00-A497-7E44-A974-7A7B94F2FC18}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
-  <si>
-    <t>Add rows here as you encounter new file name variants</t>
-  </si>
-  <si>
-    <t>filename_pattern</t>
-  </si>
-  <si>
-    <t>maps_to_doc_type</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>condition report</t>
-  </si>
-  <si>
-    <t>condition_report</t>
-  </si>
-  <si>
-    <t>cond report</t>
-  </si>
-  <si>
-    <t>survey report</t>
-  </si>
-  <si>
-    <t>inspection report</t>
-  </si>
-  <si>
-    <t>site survey</t>
-  </si>
-  <si>
-    <t>scope of works</t>
-  </si>
-  <si>
-    <t>scope_of_works</t>
-  </si>
-  <si>
-    <t>schedule of works</t>
-  </si>
-  <si>
-    <t>sow</t>
-  </si>
-  <si>
-    <t>specification</t>
-  </si>
-  <si>
-    <t>Sometimes also product_spec — check content</t>
-  </si>
-  <si>
-    <t>tender</t>
-  </si>
-  <si>
-    <t>final tender</t>
-  </si>
-  <si>
-    <t>quotation</t>
-  </si>
-  <si>
-    <t>quote</t>
-  </si>
-  <si>
-    <t>pricing sheet</t>
-  </si>
-  <si>
-    <t>pricing_sheet</t>
-  </si>
-  <si>
-    <t>price workings</t>
-  </si>
-  <si>
-    <t>build up</t>
-  </si>
-  <si>
-    <t>labour rates</t>
-  </si>
-  <si>
-    <t>labour_rates</t>
-  </si>
-  <si>
-    <t>rates</t>
-  </si>
-  <si>
-    <t>Often a sheet name in Excel</t>
-  </si>
-  <si>
-    <t>product spec</t>
-  </si>
-  <si>
-    <t>product_spec</t>
-  </si>
-  <si>
-    <t>manufacturer spec</t>
-  </si>
-  <si>
-    <t>proteus spec</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -240,34 +115,93 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -587,223 +521,531 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F6A254E-5A59-A54B-9E69-775FEB97ECD5}">
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="7"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="7"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="7"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="7"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="7"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="7"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="7"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="7"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="7"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="7"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="7"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="7"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="7"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="7"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="7"/>
+    <row r="1" ht="21.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Add rows here as you encounter new file name variants</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>filename_pattern</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>maps_to_doc_type</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>condition report</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>condition_report</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>cond report</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>condition_report</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>survey report</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>condition_report</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>inspection report</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>condition_report</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>site survey</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>condition_report</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>scope of works</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>scope_of_works</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>schedule of works</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>scope_of_works</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>sow</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>scope_of_works</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>specification</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>scope_of_works</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Sometimes also product_spec — check content</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>final tender</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>quotation</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Disambiguation: 'quote' is overloaded. Client-issued PRS/Profix quote (e.g. 'Quote_PRS...', 'PRS Quote') = tender; vendor Scaffold/Abseiler quote = subcontractor_quote; SalesQuotation/supplier merchant quote = manufacturer_pricing. Check the filename qualifier and folder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>pricing sheet</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>pricing_sheet</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>price workings</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>pricing_sheet</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>build up</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>pricing_sheet</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>labour rates</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>labour_rates</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>rates</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>labour_rates</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Often a sheet name in Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>product spec</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>product_spec</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>manufacturer spec</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>product_spec</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>proteus spec</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>product_spec</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q_</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>manufacturer_pricing</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Project-specific manufacturer quote (e.g. Q_2221717_Tradewinds_PFUPB). Also covers 'Q_Self Generated Works' from Profix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OS_</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>manufacturer_pricing</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Open / standing manufacturer price schedule (Ancillary Products, Trims, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S_</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>product_spec</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>S_&lt;projno&gt;_&lt;project&gt;_&lt;system&gt; = product specification (e.g. S_2223975_1-4 Langley Court_PCB). S_&lt;product-group&gt; (e.g. S_Ancillary Products, S_Trims) = manufacturer_pricing schedule, NOT a spec. Disambiguate by what follows S_: project number =&gt; spec; product-group word =&gt; pricing schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CR_</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>condition_report</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Standard Proteus condition report filename prefix (e.g. CR_2222745_Parker-Court_260124).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>manifest.json</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>manifest_index</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pre-built document-type map shipped with some projects (e.g. Tradewinds). Useful as a hint; verify against actual files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>tender_process_report</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>process_report</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tender process report — Profix internal record of how the tender was put together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>salesquotation</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>manufacturer_pricing</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Supplier / merchant sales quotation (e.g. JJ Roofing Supplies SalesQuotation_SQU111469).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>technical_datasheet</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Product technical datasheet (e.g. SSQ-Del-Prado-datasheet, BBA cert, catalyst tables, TDS). Secondary input to step 05 (manufacturer_pricing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>scaffold quote</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>subcontractor_quote</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Access-trade subcontractor quotation (scaffolding, e.g. JAB Scaffold Quote QU2123, Skyline Quote).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>abseiler quote</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>subcontractor_quote</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Access-trade subcontractor quotation (abseilers, e.g. FA-25410-Q1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>quote_prs</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Profix-issued client quotation (canonical Profix naming, e.g. Quote_PRS04_03-090629). Counterpart to PRS Tender.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>prs quote</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Profix-issued client quotation (e.g. PRS Quote No_25:04-090629). Same as Quote_PRS.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
